--- a/Data/EXCEL/Transfer/salemon/202512/6983-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/6983-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBC8DFD8-905D-4D21-AA5F-982725CAB937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35A110A4-DB3A-45BA-A0A3-C1C9D8A723C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{2CC10BEA-ED04-474E-8556-A2F4E13C6C3A}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{331AFF55-9C7B-4749-9829-987A32674987}"/>
   </bookViews>
   <sheets>
     <sheet name="6983-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -261,7 +261,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF008000"/>
+      <color rgb="FFFF0000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -277,7 +277,7 @@
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF008000"/>
       <name val="新細明體"/>
       <family val="2"/>
       <charset val="136"/>
@@ -857,13 +857,13 @@
     <xf numFmtId="0" fontId="18" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1258,19 +1258,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FE949D4-6B4A-4EF2-823C-636F2DBA27EE}">
-  <dimension ref="A1:Q33"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C2A08BB-3D26-437E-9D2F-7CA28714DA89}">
+  <dimension ref="A1:Q34"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.75" customWidth="1"/>
-    <col min="2" max="5" width="11.5" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="12.625" customWidth="1"/>
-    <col min="8" max="10" width="13.25" customWidth="1"/>
-    <col min="11" max="11" width="11.5" customWidth="1"/>
-    <col min="12" max="15" width="13.25" customWidth="1"/>
-    <col min="16" max="16" width="11.5" customWidth="1"/>
-    <col min="17" max="17" width="14.375" customWidth="1"/>
+    <col min="1" max="1" width="8.5" customWidth="1"/>
+    <col min="2" max="5" width="7.125" customWidth="1"/>
+    <col min="6" max="6" width="6.75" customWidth="1"/>
+    <col min="7" max="7" width="7.875" customWidth="1"/>
+    <col min="8" max="10" width="8.125" customWidth="1"/>
+    <col min="11" max="11" width="7.125" customWidth="1"/>
+    <col min="12" max="15" width="8.125" customWidth="1"/>
+    <col min="16" max="16" width="7.125" customWidth="1"/>
+    <col min="17" max="17" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1423,1385 +1423,1385 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="C5" s="6">
-        <v>132</v>
+        <v>180</v>
       </c>
       <c r="D5" s="6">
-        <v>146</v>
+        <v>186</v>
       </c>
       <c r="E5" s="6">
-        <v>127.5</v>
+        <v>126</v>
       </c>
       <c r="F5" s="7">
-        <v>-8</v>
+        <v>48</v>
       </c>
       <c r="G5" s="7">
-        <v>-5.71</v>
+        <v>36.36</v>
       </c>
       <c r="H5" s="8">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="I5" s="7">
-        <v>-33.5</v>
-      </c>
-      <c r="J5" s="7">
-        <v>-54.2</v>
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="I5" s="9">
+        <v>-89.1</v>
+      </c>
+      <c r="J5" s="9">
+        <v>-89.4</v>
       </c>
       <c r="K5" s="8">
-        <v>3.09</v>
-      </c>
-      <c r="L5" s="9">
-        <v>38.1</v>
+        <v>3.12</v>
+      </c>
+      <c r="L5" s="7">
+        <v>24.4</v>
       </c>
       <c r="M5" s="8">
-        <v>0.26100000000000001</v>
-      </c>
-      <c r="N5" s="7">
-        <v>-33.5</v>
-      </c>
-      <c r="O5" s="7">
-        <v>-54.2</v>
+        <v>2.8500000000000001E-2</v>
+      </c>
+      <c r="N5" s="9">
+        <v>-89.1</v>
+      </c>
+      <c r="O5" s="9">
+        <v>-89.4</v>
       </c>
       <c r="P5" s="8">
-        <v>3.09</v>
-      </c>
-      <c r="Q5" s="9">
-        <v>38.1</v>
+        <v>3.12</v>
+      </c>
+      <c r="Q5" s="7">
+        <v>24.4</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>141.5</v>
+        <v>140</v>
       </c>
       <c r="C6" s="12">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="D6" s="12">
-        <v>155.5</v>
+        <v>146</v>
       </c>
       <c r="E6" s="12">
-        <v>128.5</v>
+        <v>127.5</v>
       </c>
       <c r="F6" s="13">
-        <v>-1.5</v>
+        <v>-8</v>
       </c>
       <c r="G6" s="13">
-        <v>-1.06</v>
+        <v>-5.71</v>
       </c>
       <c r="H6" s="14">
-        <v>0.39300000000000002</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="I6" s="13">
-        <v>-53.3</v>
-      </c>
-      <c r="J6" s="15">
-        <v>345.4</v>
+        <v>-33.5</v>
+      </c>
+      <c r="J6" s="13">
+        <v>-54.2</v>
       </c>
       <c r="K6" s="14">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="L6" s="15">
-        <v>69.599999999999994</v>
+        <v>38.1</v>
       </c>
       <c r="M6" s="14">
-        <v>0.39300000000000002</v>
+        <v>0.26100000000000001</v>
       </c>
       <c r="N6" s="13">
-        <v>-53.3</v>
-      </c>
-      <c r="O6" s="15">
-        <v>345.4</v>
+        <v>-33.5</v>
+      </c>
+      <c r="O6" s="13">
+        <v>-54.2</v>
       </c>
       <c r="P6" s="14">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="Q6" s="15">
-        <v>69.599999999999994</v>
+        <v>38.1</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>138</v>
+        <v>141.5</v>
       </c>
       <c r="C7" s="6">
-        <v>141.5</v>
+        <v>140</v>
       </c>
       <c r="D7" s="6">
-        <v>158.5</v>
+        <v>155.5</v>
       </c>
       <c r="E7" s="6">
-        <v>131.5</v>
+        <v>128.5</v>
       </c>
       <c r="F7" s="9">
-        <v>3.5</v>
+        <v>-1.5</v>
       </c>
       <c r="G7" s="9">
-        <v>2.54</v>
+        <v>-1.06</v>
       </c>
       <c r="H7" s="8">
-        <v>0.84199999999999997</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="I7" s="9">
-        <v>192.3</v>
-      </c>
-      <c r="J7" s="9">
-        <v>2387.8000000000002</v>
+        <v>-53.3</v>
+      </c>
+      <c r="J7" s="7">
+        <v>345.4</v>
       </c>
       <c r="K7" s="8">
-        <v>2.44</v>
-      </c>
-      <c r="L7" s="9">
-        <v>54.2</v>
+        <v>2.83</v>
+      </c>
+      <c r="L7" s="7">
+        <v>69.599999999999994</v>
       </c>
       <c r="M7" s="8">
-        <v>0.84199999999999997</v>
+        <v>0.39300000000000002</v>
       </c>
       <c r="N7" s="9">
-        <v>192.3</v>
-      </c>
-      <c r="O7" s="9">
-        <v>2387.8000000000002</v>
+        <v>-53.3</v>
+      </c>
+      <c r="O7" s="7">
+        <v>345.4</v>
       </c>
       <c r="P7" s="8">
-        <v>2.44</v>
-      </c>
-      <c r="Q7" s="9">
-        <v>54.2</v>
+        <v>2.83</v>
+      </c>
+      <c r="Q7" s="7">
+        <v>69.599999999999994</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>105.5</v>
+        <v>138</v>
       </c>
       <c r="C8" s="12">
-        <v>138</v>
+        <v>141.5</v>
       </c>
       <c r="D8" s="12">
-        <v>138</v>
+        <v>158.5</v>
       </c>
       <c r="E8" s="12">
-        <v>105.5</v>
+        <v>131.5</v>
       </c>
       <c r="F8" s="15">
-        <v>32.5</v>
+        <v>3.5</v>
       </c>
       <c r="G8" s="15">
-        <v>30.81</v>
+        <v>2.54</v>
       </c>
       <c r="H8" s="14">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="I8" s="13">
-        <v>-9.65</v>
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="I8" s="15">
+        <v>192.3</v>
       </c>
       <c r="J8" s="15">
-        <v>560.1</v>
+        <v>2387.8000000000002</v>
       </c>
       <c r="K8" s="14">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="L8" s="15">
-        <v>3.24</v>
+        <v>54.2</v>
       </c>
       <c r="M8" s="14">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="N8" s="13">
-        <v>-9.65</v>
+        <v>0.84199999999999997</v>
+      </c>
+      <c r="N8" s="15">
+        <v>192.3</v>
       </c>
       <c r="O8" s="15">
-        <v>560.1</v>
+        <v>2387.8000000000002</v>
       </c>
       <c r="P8" s="14">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" s="15">
-        <v>3.24</v>
+        <v>54.2</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>103</v>
+        <v>105.5</v>
       </c>
       <c r="C9" s="6">
+        <v>138</v>
+      </c>
+      <c r="D9" s="6">
+        <v>138</v>
+      </c>
+      <c r="E9" s="6">
         <v>105.5</v>
       </c>
-      <c r="D9" s="6">
-        <v>107.5</v>
-      </c>
-      <c r="E9" s="6">
-        <v>99.3</v>
-      </c>
-      <c r="F9" s="9">
-        <v>2.5</v>
-      </c>
-      <c r="G9" s="9">
-        <v>2.4300000000000002</v>
+      <c r="F9" s="7">
+        <v>32.5</v>
+      </c>
+      <c r="G9" s="7">
+        <v>30.81</v>
       </c>
       <c r="H9" s="8">
-        <v>0.31900000000000001</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="I9" s="9">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="J9" s="9">
-        <v>124.6</v>
+        <v>-9.65</v>
+      </c>
+      <c r="J9" s="7">
+        <v>560.1</v>
       </c>
       <c r="K9" s="8">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="L9" s="7">
-        <v>-12.9</v>
+        <v>3.24</v>
       </c>
       <c r="M9" s="8">
-        <v>0.31900000000000001</v>
+        <v>0.28799999999999998</v>
       </c>
       <c r="N9" s="9">
-        <v>78.099999999999994</v>
-      </c>
-      <c r="O9" s="9">
-        <v>124.6</v>
+        <v>-9.65</v>
+      </c>
+      <c r="O9" s="7">
+        <v>560.1</v>
       </c>
       <c r="P9" s="8">
-        <v>1.31</v>
+        <v>1.6</v>
       </c>
       <c r="Q9" s="7">
-        <v>-12.9</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="C10" s="12">
-        <v>103</v>
+        <v>105.5</v>
       </c>
       <c r="D10" s="12">
         <v>107.5</v>
       </c>
       <c r="E10" s="12">
-        <v>102.5</v>
-      </c>
-      <c r="F10" s="13">
-        <v>-6</v>
-      </c>
-      <c r="G10" s="13">
-        <v>-5.5</v>
+        <v>99.3</v>
+      </c>
+      <c r="F10" s="15">
+        <v>2.5</v>
+      </c>
+      <c r="G10" s="15">
+        <v>2.4300000000000002</v>
       </c>
       <c r="H10" s="14">
-        <v>0.17899999999999999</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="I10" s="15">
-        <v>116.6</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="J10" s="15">
-        <v>251.5</v>
+        <v>124.6</v>
       </c>
       <c r="K10" s="14">
-        <v>0.99199999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="L10" s="13">
-        <v>-27.2</v>
+        <v>-12.9</v>
       </c>
       <c r="M10" s="14">
-        <v>0.17899999999999999</v>
+        <v>0.31900000000000001</v>
       </c>
       <c r="N10" s="15">
-        <v>116.6</v>
+        <v>78.099999999999994</v>
       </c>
       <c r="O10" s="15">
-        <v>251.5</v>
+        <v>124.6</v>
       </c>
       <c r="P10" s="14">
-        <v>0.99199999999999999</v>
+        <v>1.31</v>
       </c>
       <c r="Q10" s="13">
-        <v>-27.2</v>
+        <v>-12.9</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>108.5</v>
+        <v>109</v>
       </c>
       <c r="C11" s="6">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="D11" s="6">
-        <v>110</v>
+        <v>107.5</v>
       </c>
       <c r="E11" s="6">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="F11" s="9">
-        <v>0.5</v>
+        <v>-6</v>
       </c>
       <c r="G11" s="9">
-        <v>0.46</v>
+        <v>-5.5</v>
       </c>
       <c r="H11" s="8">
-        <v>8.2600000000000007E-2</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="I11" s="7">
-        <v>-56.7</v>
+        <v>116.6</v>
       </c>
       <c r="J11" s="7">
-        <v>-84.8</v>
+        <v>251.5</v>
       </c>
       <c r="K11" s="8">
-        <v>0.81299999999999994</v>
-      </c>
-      <c r="L11" s="7">
-        <v>-38</v>
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="L11" s="9">
+        <v>-27.2</v>
       </c>
       <c r="M11" s="8">
-        <v>8.2600000000000007E-2</v>
+        <v>0.17899999999999999</v>
       </c>
       <c r="N11" s="7">
-        <v>-56.7</v>
+        <v>116.6</v>
       </c>
       <c r="O11" s="7">
-        <v>-84.8</v>
+        <v>251.5</v>
       </c>
       <c r="P11" s="8">
-        <v>0.81299999999999994</v>
-      </c>
-      <c r="Q11" s="7">
-        <v>-38</v>
+        <v>0.99199999999999999</v>
+      </c>
+      <c r="Q11" s="9">
+        <v>-27.2</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="12">
-        <v>118</v>
+        <v>108.5</v>
       </c>
       <c r="C12" s="12">
-        <v>108.5</v>
+        <v>109</v>
       </c>
       <c r="D12" s="12">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="E12" s="12">
-        <v>96.9</v>
-      </c>
-      <c r="F12" s="13">
-        <v>-9.5</v>
-      </c>
-      <c r="G12" s="13">
-        <v>-8.0500000000000007</v>
+        <v>103.5</v>
+      </c>
+      <c r="F12" s="15">
+        <v>0.5</v>
+      </c>
+      <c r="G12" s="15">
+        <v>0.46</v>
       </c>
       <c r="H12" s="14">
-        <v>0.191</v>
+        <v>8.2600000000000007E-2</v>
       </c>
       <c r="I12" s="13">
-        <v>-51.5</v>
-      </c>
-      <c r="J12" s="15">
-        <v>721.4</v>
+        <v>-56.7</v>
+      </c>
+      <c r="J12" s="13">
+        <v>-84.8</v>
       </c>
       <c r="K12" s="14">
-        <v>0.73099999999999998</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="L12" s="13">
-        <v>-4.96</v>
+        <v>-38</v>
       </c>
       <c r="M12" s="14">
-        <v>0.191</v>
+        <v>8.2600000000000007E-2</v>
       </c>
       <c r="N12" s="13">
-        <v>-51.5</v>
-      </c>
-      <c r="O12" s="15">
-        <v>721.4</v>
+        <v>-56.7</v>
+      </c>
+      <c r="O12" s="13">
+        <v>-84.8</v>
       </c>
       <c r="P12" s="14">
-        <v>0.73099999999999998</v>
+        <v>0.81299999999999994</v>
       </c>
       <c r="Q12" s="13">
-        <v>-4.96</v>
+        <v>-38</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C13" s="6">
-        <v>118</v>
+        <v>108.5</v>
       </c>
       <c r="D13" s="6">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="E13" s="6">
-        <v>116</v>
-      </c>
-      <c r="F13" s="7">
-        <v>-4</v>
-      </c>
-      <c r="G13" s="7">
-        <v>-3.28</v>
+        <v>96.9</v>
+      </c>
+      <c r="F13" s="9">
+        <v>-9.5</v>
+      </c>
+      <c r="G13" s="9">
+        <v>-8.0500000000000007</v>
       </c>
       <c r="H13" s="8">
-        <v>0.39400000000000002</v>
+        <v>0.191</v>
       </c>
       <c r="I13" s="9">
-        <v>2534.1</v>
-      </c>
-      <c r="J13" s="9">
-        <v>497.6</v>
+        <v>-51.5</v>
+      </c>
+      <c r="J13" s="7">
+        <v>721.4</v>
       </c>
       <c r="K13" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="L13" s="7">
-        <v>-27.6</v>
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="L13" s="9">
+        <v>-4.96</v>
       </c>
       <c r="M13" s="8">
-        <v>0.39400000000000002</v>
+        <v>0.191</v>
       </c>
       <c r="N13" s="9">
-        <v>2534.1</v>
-      </c>
-      <c r="O13" s="9">
-        <v>497.6</v>
+        <v>-51.5</v>
+      </c>
+      <c r="O13" s="7">
+        <v>721.4</v>
       </c>
       <c r="P13" s="8">
-        <v>0.54</v>
-      </c>
-      <c r="Q13" s="7">
-        <v>-27.6</v>
+        <v>0.73099999999999998</v>
+      </c>
+      <c r="Q13" s="9">
+        <v>-4.96</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="12">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C14" s="12">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D14" s="12">
         <v>125</v>
       </c>
       <c r="E14" s="12">
-        <v>114</v>
-      </c>
-      <c r="F14" s="15">
-        <v>7</v>
-      </c>
-      <c r="G14" s="15">
-        <v>6.09</v>
+        <v>116</v>
+      </c>
+      <c r="F14" s="13">
+        <v>-4</v>
+      </c>
+      <c r="G14" s="13">
+        <v>-3.28</v>
       </c>
       <c r="H14" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="I14" s="13">
-        <v>-88.6</v>
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="I14" s="15">
+        <v>2534.1</v>
       </c>
       <c r="J14" s="15">
-        <v>6.78</v>
+        <v>497.6</v>
       </c>
       <c r="K14" s="14">
-        <v>0.14599999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="L14" s="13">
-        <v>-78.5</v>
+        <v>-27.6</v>
       </c>
       <c r="M14" s="14">
-        <v>1.4999999999999999E-2</v>
-      </c>
-      <c r="N14" s="13">
-        <v>-88.6</v>
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="N14" s="15">
+        <v>2534.1</v>
       </c>
       <c r="O14" s="15">
-        <v>6.78</v>
+        <v>497.6</v>
       </c>
       <c r="P14" s="14">
-        <v>0.14599999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="Q14" s="13">
-        <v>-78.5</v>
+        <v>-27.6</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
         <v>115</v>
       </c>
       <c r="C15" s="6">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="D15" s="6">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E15" s="6">
-        <v>111</v>
-      </c>
-      <c r="F15" s="8">
-        <v>0</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0</v>
+        <v>114</v>
+      </c>
+      <c r="F15" s="7">
+        <v>7</v>
+      </c>
+      <c r="G15" s="7">
+        <v>6.09</v>
       </c>
       <c r="H15" s="8">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="I15" s="7">
-        <v>-51.3</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="I15" s="9">
+        <v>-88.6</v>
       </c>
       <c r="J15" s="7">
-        <v>-80.3</v>
+        <v>6.78</v>
       </c>
       <c r="K15" s="8">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="L15" s="7">
-        <v>-80.3</v>
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="L15" s="9">
+        <v>-78.5</v>
       </c>
       <c r="M15" s="8">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="N15" s="7">
-        <v>-51.3</v>
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N15" s="9">
+        <v>-88.6</v>
       </c>
       <c r="O15" s="7">
-        <v>-80.3</v>
+        <v>6.78</v>
       </c>
       <c r="P15" s="8">
-        <v>0.13100000000000001</v>
-      </c>
-      <c r="Q15" s="7">
-        <v>-80.3</v>
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="Q15" s="9">
+        <v>-78.5</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="12">
-        <v>103</v>
+        <v>115</v>
       </c>
       <c r="C16" s="12">
         <v>115</v>
       </c>
       <c r="D16" s="12">
-        <v>119.5</v>
+        <v>118</v>
       </c>
       <c r="E16" s="12">
-        <v>99.8</v>
-      </c>
-      <c r="F16" s="15">
-        <v>12</v>
-      </c>
-      <c r="G16" s="15">
-        <v>11.65</v>
+        <v>111</v>
+      </c>
+      <c r="F16" s="14">
+        <v>0</v>
+      </c>
+      <c r="G16" s="14">
+        <v>0</v>
       </c>
       <c r="H16" s="14">
-        <v>0.26900000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="I16" s="13">
-        <v>-52.9</v>
+        <v>-51.3</v>
       </c>
       <c r="J16" s="13">
-        <v>-41.8</v>
+        <v>-80.3</v>
       </c>
       <c r="K16" s="14">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="L16" s="15">
-        <v>40.799999999999997</v>
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="L16" s="13">
+        <v>-80.3</v>
       </c>
       <c r="M16" s="14">
-        <v>0.26900000000000002</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="N16" s="13">
-        <v>-52.9</v>
+        <v>-51.3</v>
       </c>
       <c r="O16" s="13">
-        <v>-41.8</v>
+        <v>-80.3</v>
       </c>
       <c r="P16" s="14">
-        <v>2.5099999999999998</v>
-      </c>
-      <c r="Q16" s="15">
-        <v>40.799999999999997</v>
+        <v>0.13100000000000001</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>-80.3</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B17" s="6">
+        <v>103</v>
+      </c>
+      <c r="C17" s="6">
         <v>115</v>
       </c>
-      <c r="C17" s="6">
-        <v>103</v>
-      </c>
       <c r="D17" s="6">
-        <v>115</v>
+        <v>119.5</v>
       </c>
       <c r="E17" s="6">
-        <v>100</v>
+        <v>99.8</v>
       </c>
       <c r="F17" s="7">
-        <v>-12</v>
+        <v>12</v>
       </c>
       <c r="G17" s="7">
-        <v>-10.43</v>
+        <v>11.65</v>
       </c>
       <c r="H17" s="8">
-        <v>0.56999999999999995</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="I17" s="9">
-        <v>547</v>
+        <v>-52.9</v>
       </c>
       <c r="J17" s="9">
-        <v>1277.5999999999999</v>
+        <v>-41.8</v>
       </c>
       <c r="K17" s="8">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="L17" s="9">
-        <v>69.7</v>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="L17" s="7">
+        <v>40.799999999999997</v>
       </c>
       <c r="M17" s="8">
-        <v>0.56999999999999995</v>
+        <v>0.26900000000000002</v>
       </c>
       <c r="N17" s="9">
-        <v>547</v>
+        <v>-52.9</v>
       </c>
       <c r="O17" s="9">
-        <v>1277.5999999999999</v>
+        <v>-41.8</v>
       </c>
       <c r="P17" s="8">
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="Q17" s="9">
-        <v>69.7</v>
+        <v>2.5099999999999998</v>
+      </c>
+      <c r="Q17" s="7">
+        <v>40.799999999999997</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="12">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C18" s="12">
+        <v>103</v>
+      </c>
+      <c r="D18" s="12">
         <v>115</v>
       </c>
-      <c r="D18" s="12">
-        <v>117</v>
-      </c>
       <c r="E18" s="12">
-        <v>97.9</v>
+        <v>100</v>
       </c>
       <c r="F18" s="13">
-        <v>-3</v>
+        <v>-12</v>
       </c>
       <c r="G18" s="13">
-        <v>-2.54</v>
+        <v>-10.43</v>
       </c>
       <c r="H18" s="14">
-        <v>8.8200000000000001E-2</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="I18" s="15">
-        <v>160.6</v>
-      </c>
-      <c r="J18" s="13">
-        <v>-22.9</v>
+        <v>547</v>
+      </c>
+      <c r="J18" s="15">
+        <v>1277.5999999999999</v>
       </c>
       <c r="K18" s="14">
-        <v>1.67</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="L18" s="15">
-        <v>30.6</v>
+        <v>69.7</v>
       </c>
       <c r="M18" s="14">
-        <v>8.8200000000000001E-2</v>
+        <v>0.56999999999999995</v>
       </c>
       <c r="N18" s="15">
-        <v>160.6</v>
-      </c>
-      <c r="O18" s="13">
-        <v>-22.9</v>
+        <v>547</v>
+      </c>
+      <c r="O18" s="15">
+        <v>1277.5999999999999</v>
       </c>
       <c r="P18" s="14">
-        <v>1.67</v>
+        <v>2.2400000000000002</v>
       </c>
       <c r="Q18" s="15">
-        <v>30.6</v>
+        <v>69.7</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="6">
-        <v>120.5</v>
+        <v>118</v>
       </c>
       <c r="C19" s="6">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D19" s="6">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E19" s="6">
-        <v>112.5</v>
-      </c>
-      <c r="F19" s="7">
-        <v>-2.5</v>
-      </c>
-      <c r="G19" s="7">
-        <v>-2.0699999999999998</v>
+        <v>97.9</v>
+      </c>
+      <c r="F19" s="9">
+        <v>-3</v>
+      </c>
+      <c r="G19" s="9">
+        <v>-2.54</v>
       </c>
       <c r="H19" s="8">
-        <v>3.3799999999999997E-2</v>
+        <v>8.8200000000000001E-2</v>
       </c>
       <c r="I19" s="7">
-        <v>-22.4</v>
+        <v>160.6</v>
       </c>
       <c r="J19" s="9">
-        <v>295.2</v>
+        <v>-22.9</v>
       </c>
       <c r="K19" s="8">
-        <v>1.58</v>
-      </c>
-      <c r="L19" s="9">
-        <v>35.9</v>
+        <v>1.67</v>
+      </c>
+      <c r="L19" s="7">
+        <v>30.6</v>
       </c>
       <c r="M19" s="8">
-        <v>3.3799999999999997E-2</v>
+        <v>8.8200000000000001E-2</v>
       </c>
       <c r="N19" s="7">
-        <v>-22.4</v>
+        <v>160.6</v>
       </c>
       <c r="O19" s="9">
-        <v>295.2</v>
+        <v>-22.9</v>
       </c>
       <c r="P19" s="8">
-        <v>1.58</v>
-      </c>
-      <c r="Q19" s="9">
-        <v>35.9</v>
+        <v>1.67</v>
+      </c>
+      <c r="Q19" s="7">
+        <v>30.6</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="12">
-        <v>134</v>
+        <v>120.5</v>
       </c>
       <c r="C20" s="12">
-        <v>120.5</v>
+        <v>118</v>
       </c>
       <c r="D20" s="12">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="E20" s="12">
-        <v>116</v>
+        <v>112.5</v>
       </c>
       <c r="F20" s="13">
-        <v>-13.5</v>
+        <v>-2.5</v>
       </c>
       <c r="G20" s="13">
-        <v>-10.07</v>
+        <v>-2.0699999999999998</v>
       </c>
       <c r="H20" s="14">
-        <v>4.36E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="I20" s="13">
-        <v>-69.3</v>
+        <v>-22.4</v>
       </c>
       <c r="J20" s="15">
-        <v>1603.5</v>
+        <v>295.2</v>
       </c>
       <c r="K20" s="14">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="L20" s="15">
-        <v>34</v>
+        <v>35.9</v>
       </c>
       <c r="M20" s="14">
-        <v>4.36E-2</v>
+        <v>3.3799999999999997E-2</v>
       </c>
       <c r="N20" s="13">
-        <v>-69.3</v>
+        <v>-22.4</v>
       </c>
       <c r="O20" s="15">
-        <v>1603.5</v>
+        <v>295.2</v>
       </c>
       <c r="P20" s="14">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Q20" s="15">
-        <v>34</v>
+        <v>35.9</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="6">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="C21" s="6">
+        <v>120.5</v>
+      </c>
+      <c r="D21" s="6">
         <v>134</v>
       </c>
-      <c r="D21" s="6">
-        <v>137</v>
-      </c>
       <c r="E21" s="6">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F21" s="9">
-        <v>10</v>
+        <v>-13.5</v>
       </c>
       <c r="G21" s="9">
-        <v>8.06</v>
+        <v>-10.07</v>
       </c>
       <c r="H21" s="8">
-        <v>0.14199999999999999</v>
+        <v>4.36E-2</v>
       </c>
       <c r="I21" s="9">
-        <v>178.7</v>
-      </c>
-      <c r="J21" s="9">
-        <v>197.6</v>
+        <v>-69.3</v>
+      </c>
+      <c r="J21" s="7">
+        <v>1603.5</v>
       </c>
       <c r="K21" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="L21" s="9">
-        <v>30.5</v>
+        <v>1.55</v>
+      </c>
+      <c r="L21" s="7">
+        <v>34</v>
       </c>
       <c r="M21" s="8">
-        <v>0.14199999999999999</v>
+        <v>4.36E-2</v>
       </c>
       <c r="N21" s="9">
-        <v>178.7</v>
-      </c>
-      <c r="O21" s="9">
-        <v>197.6</v>
+        <v>-69.3</v>
+      </c>
+      <c r="O21" s="7">
+        <v>1603.5</v>
       </c>
       <c r="P21" s="8">
-        <v>1.5</v>
-      </c>
-      <c r="Q21" s="9">
-        <v>30.5</v>
+        <v>1.55</v>
+      </c>
+      <c r="Q21" s="7">
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="12">
-        <v>87.5</v>
+        <v>124</v>
       </c>
       <c r="C22" s="12">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="D22" s="12">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="E22" s="12">
-        <v>83</v>
+        <v>120</v>
       </c>
       <c r="F22" s="15">
-        <v>36.5</v>
+        <v>10</v>
       </c>
       <c r="G22" s="15">
-        <v>41.71</v>
+        <v>8.06</v>
       </c>
       <c r="H22" s="14">
-        <v>5.0900000000000001E-2</v>
-      </c>
-      <c r="I22" s="13">
-        <v>-90.6</v>
-      </c>
-      <c r="J22" s="13">
-        <v>-77.8</v>
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="I22" s="15">
+        <v>178.7</v>
+      </c>
+      <c r="J22" s="15">
+        <v>197.6</v>
       </c>
       <c r="K22" s="14">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="L22" s="15">
-        <v>23.3</v>
+        <v>30.5</v>
       </c>
       <c r="M22" s="14">
-        <v>5.0900000000000001E-2</v>
-      </c>
-      <c r="N22" s="13">
-        <v>-90.6</v>
-      </c>
-      <c r="O22" s="13">
-        <v>-77.8</v>
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="N22" s="15">
+        <v>178.7</v>
+      </c>
+      <c r="O22" s="15">
+        <v>197.6</v>
       </c>
       <c r="P22" s="14">
-        <v>1.36</v>
+        <v>1.5</v>
       </c>
       <c r="Q22" s="15">
-        <v>23.3</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="6">
-        <v>103</v>
+        <v>87.5</v>
       </c>
       <c r="C23" s="6">
-        <v>87.5</v>
+        <v>124</v>
       </c>
       <c r="D23" s="6">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="E23" s="6">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F23" s="7">
-        <v>-15.5</v>
+        <v>36.5</v>
       </c>
       <c r="G23" s="7">
-        <v>-15.05</v>
+        <v>41.71</v>
       </c>
       <c r="H23" s="8">
-        <v>0.54300000000000004</v>
+        <v>5.0900000000000001E-2</v>
       </c>
       <c r="I23" s="9">
-        <v>2236.4</v>
+        <v>-90.6</v>
       </c>
       <c r="J23" s="9">
-        <v>12.8</v>
+        <v>-77.8</v>
       </c>
       <c r="K23" s="8">
-        <v>1.31</v>
-      </c>
-      <c r="L23" s="9">
-        <v>49.6</v>
+        <v>1.36</v>
+      </c>
+      <c r="L23" s="7">
+        <v>23.3</v>
       </c>
       <c r="M23" s="8">
-        <v>0.54300000000000004</v>
+        <v>5.0900000000000001E-2</v>
       </c>
       <c r="N23" s="9">
-        <v>2236.4</v>
+        <v>-90.6</v>
       </c>
       <c r="O23" s="9">
-        <v>12.8</v>
+        <v>-77.8</v>
       </c>
       <c r="P23" s="8">
-        <v>1.31</v>
-      </c>
-      <c r="Q23" s="9">
-        <v>49.6</v>
+        <v>1.36</v>
+      </c>
+      <c r="Q23" s="7">
+        <v>23.3</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="12">
-        <v>101.5</v>
+        <v>103</v>
       </c>
       <c r="C24" s="12">
-        <v>103</v>
+        <v>87.5</v>
       </c>
       <c r="D24" s="12">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="E24" s="12">
-        <v>99</v>
-      </c>
-      <c r="F24" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="G24" s="15">
-        <v>1.48</v>
+        <v>86</v>
+      </c>
+      <c r="F24" s="13">
+        <v>-15.5</v>
+      </c>
+      <c r="G24" s="13">
+        <v>-15.05</v>
       </c>
       <c r="H24" s="14">
-        <v>2.3199999999999998E-2</v>
-      </c>
-      <c r="I24" s="13">
-        <v>-64.7</v>
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="I24" s="15">
+        <v>2236.4</v>
       </c>
       <c r="J24" s="15">
-        <v>3840.7</v>
+        <v>12.8</v>
       </c>
       <c r="K24" s="14">
-        <v>0.76900000000000002</v>
+        <v>1.31</v>
       </c>
       <c r="L24" s="15">
-        <v>94.6</v>
+        <v>49.6</v>
       </c>
       <c r="M24" s="14">
-        <v>2.3199999999999998E-2</v>
-      </c>
-      <c r="N24" s="13">
-        <v>-64.7</v>
+        <v>0.54300000000000004</v>
+      </c>
+      <c r="N24" s="15">
+        <v>2236.4</v>
       </c>
       <c r="O24" s="15">
-        <v>3840.7</v>
+        <v>12.8</v>
       </c>
       <c r="P24" s="14">
-        <v>0.76900000000000002</v>
+        <v>1.31</v>
       </c>
       <c r="Q24" s="15">
-        <v>94.6</v>
+        <v>49.6</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="6">
+        <v>101.5</v>
+      </c>
+      <c r="C25" s="6">
+        <v>103</v>
+      </c>
+      <c r="D25" s="6">
         <v>125</v>
       </c>
-      <c r="C25" s="6">
-        <v>101.5</v>
-      </c>
-      <c r="D25" s="6">
-        <v>123</v>
-      </c>
       <c r="E25" s="6">
-        <v>96.5</v>
+        <v>99</v>
       </c>
       <c r="F25" s="7">
-        <v>-23.5</v>
+        <v>1.5</v>
       </c>
       <c r="G25" s="7">
-        <v>-18.8</v>
+        <v>1.48</v>
       </c>
       <c r="H25" s="8">
-        <v>6.59E-2</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="I25" s="9">
-        <v>370.7</v>
-      </c>
-      <c r="J25" s="9">
-        <v>101.1</v>
+        <v>-64.7</v>
+      </c>
+      <c r="J25" s="7">
+        <v>3840.7</v>
       </c>
       <c r="K25" s="8">
-        <v>0.746</v>
-      </c>
-      <c r="L25" s="9">
-        <v>89</v>
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="L25" s="7">
+        <v>94.6</v>
       </c>
       <c r="M25" s="8">
-        <v>6.59E-2</v>
+        <v>2.3199999999999998E-2</v>
       </c>
       <c r="N25" s="9">
-        <v>370.7</v>
-      </c>
-      <c r="O25" s="9">
-        <v>101.1</v>
+        <v>-64.7</v>
+      </c>
+      <c r="O25" s="7">
+        <v>3840.7</v>
       </c>
       <c r="P25" s="8">
-        <v>0.746</v>
-      </c>
-      <c r="Q25" s="9">
-        <v>89</v>
+        <v>0.76900000000000002</v>
+      </c>
+      <c r="Q25" s="7">
+        <v>94.6</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="12">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C26" s="12">
-        <v>125</v>
+        <v>101.5</v>
       </c>
       <c r="D26" s="12">
-        <v>160</v>
+        <v>123</v>
       </c>
       <c r="E26" s="12">
-        <v>118</v>
-      </c>
-      <c r="F26" s="15">
-        <v>1</v>
-      </c>
-      <c r="G26" s="15">
-        <v>0.81</v>
+        <v>96.5</v>
+      </c>
+      <c r="F26" s="13">
+        <v>-23.5</v>
+      </c>
+      <c r="G26" s="13">
+        <v>-18.8</v>
       </c>
       <c r="H26" s="14">
-        <v>1.4E-2</v>
-      </c>
-      <c r="I26" s="13">
-        <v>-97.9</v>
-      </c>
-      <c r="J26" s="13">
-        <v>-95.7</v>
+        <v>6.59E-2</v>
+      </c>
+      <c r="I26" s="15">
+        <v>370.7</v>
+      </c>
+      <c r="J26" s="15">
+        <v>101.1</v>
       </c>
       <c r="K26" s="14">
-        <v>0.68</v>
+        <v>0.746</v>
       </c>
       <c r="L26" s="15">
-        <v>87.8</v>
+        <v>89</v>
       </c>
       <c r="M26" s="14">
-        <v>1.4E-2</v>
-      </c>
-      <c r="N26" s="13">
-        <v>-97.9</v>
-      </c>
-      <c r="O26" s="13">
-        <v>-95.7</v>
+        <v>6.59E-2</v>
+      </c>
+      <c r="N26" s="15">
+        <v>370.7</v>
+      </c>
+      <c r="O26" s="15">
+        <v>101.1</v>
       </c>
       <c r="P26" s="14">
-        <v>0.68</v>
+        <v>0.746</v>
       </c>
       <c r="Q26" s="15">
-        <v>87.8</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="6">
-        <v>79.5</v>
+        <v>124</v>
       </c>
       <c r="C27" s="6">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D27" s="6">
-        <v>125.5</v>
+        <v>160</v>
       </c>
       <c r="E27" s="6">
-        <v>74.5</v>
-      </c>
-      <c r="F27" s="9">
-        <v>44.5</v>
-      </c>
-      <c r="G27" s="9">
-        <v>55.97</v>
+        <v>118</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1</v>
+      </c>
+      <c r="G27" s="7">
+        <v>0.81</v>
       </c>
       <c r="H27" s="8">
-        <v>0.66600000000000004</v>
+        <v>1.4E-2</v>
       </c>
       <c r="I27" s="9">
-        <v>44</v>
+        <v>-97.9</v>
       </c>
       <c r="J27" s="9">
-        <v>1915.7</v>
+        <v>-95.7</v>
       </c>
       <c r="K27" s="8">
-        <v>0.66600000000000004</v>
-      </c>
-      <c r="L27" s="9">
-        <v>1915.7</v>
+        <v>0.68</v>
+      </c>
+      <c r="L27" s="7">
+        <v>87.8</v>
       </c>
       <c r="M27" s="8">
-        <v>0.66600000000000004</v>
+        <v>1.4E-2</v>
       </c>
       <c r="N27" s="9">
-        <v>44</v>
+        <v>-97.9</v>
       </c>
       <c r="O27" s="9">
-        <v>1915.7</v>
+        <v>-95.7</v>
       </c>
       <c r="P27" s="8">
-        <v>0.66600000000000004</v>
-      </c>
-      <c r="Q27" s="9">
-        <v>1915.7</v>
+        <v>0.68</v>
+      </c>
+      <c r="Q27" s="7">
+        <v>87.8</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>45261</v>
+        <v>45292</v>
       </c>
       <c r="B28" s="12">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
       <c r="C28" s="12">
-        <v>79.5</v>
+        <v>124</v>
       </c>
       <c r="D28" s="12">
-        <v>87.3</v>
+        <v>125.5</v>
       </c>
       <c r="E28" s="12">
-        <v>64.8</v>
+        <v>74.5</v>
       </c>
       <c r="F28" s="15">
-        <v>9</v>
+        <v>44.5</v>
       </c>
       <c r="G28" s="15">
-        <v>12.77</v>
+        <v>55.97</v>
       </c>
       <c r="H28" s="14">
-        <v>0.46200000000000002</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="I28" s="15">
-        <v>1016.3</v>
-      </c>
-      <c r="J28" s="13">
-        <v>-15.5</v>
+        <v>44</v>
+      </c>
+      <c r="J28" s="15">
+        <v>1915.7</v>
       </c>
       <c r="K28" s="14">
-        <v>1.78</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="L28" s="15">
-        <v>12.9</v>
+        <v>1915.7</v>
       </c>
       <c r="M28" s="14">
-        <v>0.46200000000000002</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="N28" s="15">
-        <v>1016.3</v>
-      </c>
-      <c r="O28" s="13">
-        <v>-15.5</v>
+        <v>44</v>
+      </c>
+      <c r="O28" s="15">
+        <v>1915.7</v>
       </c>
       <c r="P28" s="14">
-        <v>1.78</v>
+        <v>0.66600000000000004</v>
       </c>
       <c r="Q28" s="15">
-        <v>12.9</v>
+        <v>1915.7</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="6">
-        <v>74.5</v>
+        <v>70.5</v>
       </c>
       <c r="C29" s="6">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
       <c r="D29" s="6">
-        <v>74.5</v>
+        <v>87.3</v>
       </c>
       <c r="E29" s="6">
-        <v>65</v>
+        <v>64.8</v>
       </c>
       <c r="F29" s="7">
-        <v>-4</v>
+        <v>9</v>
       </c>
       <c r="G29" s="7">
-        <v>-5.37</v>
+        <v>12.77</v>
       </c>
       <c r="H29" s="8">
-        <v>4.1399999999999999E-2</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="I29" s="7">
-        <v>-63.8</v>
-      </c>
-      <c r="J29" s="7">
-        <v>-7.29</v>
+        <v>1016.3</v>
+      </c>
+      <c r="J29" s="9">
+        <v>-15.5</v>
       </c>
       <c r="K29" s="8">
-        <v>1.32</v>
-      </c>
-      <c r="L29" s="9">
-        <v>28</v>
+        <v>1.78</v>
+      </c>
+      <c r="L29" s="7">
+        <v>12.9</v>
       </c>
       <c r="M29" s="8">
-        <v>4.1399999999999999E-2</v>
+        <v>0.46200000000000002</v>
       </c>
       <c r="N29" s="7">
-        <v>-63.8</v>
-      </c>
-      <c r="O29" s="7">
-        <v>-7.29</v>
+        <v>1016.3</v>
+      </c>
+      <c r="O29" s="9">
+        <v>-15.5</v>
       </c>
       <c r="P29" s="8">
-        <v>1.32</v>
-      </c>
-      <c r="Q29" s="9">
-        <v>28</v>
+        <v>1.78</v>
+      </c>
+      <c r="Q29" s="7">
+        <v>12.9</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>45200</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G30" s="14" t="s">
-        <v>17</v>
+        <v>45231</v>
+      </c>
+      <c r="B30" s="12">
+        <v>74.5</v>
+      </c>
+      <c r="C30" s="12">
+        <v>70.5</v>
+      </c>
+      <c r="D30" s="12">
+        <v>74.5</v>
+      </c>
+      <c r="E30" s="12">
+        <v>65</v>
+      </c>
+      <c r="F30" s="13">
+        <v>-4</v>
+      </c>
+      <c r="G30" s="13">
+        <v>-5.37</v>
       </c>
       <c r="H30" s="14">
-        <v>0.114</v>
-      </c>
-      <c r="I30" s="15">
-        <v>1235.5999999999999</v>
-      </c>
-      <c r="J30" s="15">
-        <v>11.8</v>
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="I30" s="13">
+        <v>-63.8</v>
+      </c>
+      <c r="J30" s="13">
+        <v>-7.29</v>
       </c>
       <c r="K30" s="14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="L30" s="15">
-        <v>29.6</v>
+        <v>28</v>
       </c>
       <c r="M30" s="14">
-        <v>0.114</v>
-      </c>
-      <c r="N30" s="15">
-        <v>1235.5999999999999</v>
-      </c>
-      <c r="O30" s="15">
-        <v>11.8</v>
+        <v>4.1399999999999999E-2</v>
+      </c>
+      <c r="N30" s="13">
+        <v>-63.8</v>
+      </c>
+      <c r="O30" s="13">
+        <v>-7.29</v>
       </c>
       <c r="P30" s="14">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="Q30" s="15">
-        <v>29.6</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
@@ -2822,39 +2822,39 @@
         <v>17</v>
       </c>
       <c r="H31" s="8">
-        <v>8.6E-3</v>
-      </c>
-      <c r="I31" s="9">
-        <v>234.4</v>
+        <v>0.114</v>
+      </c>
+      <c r="I31" s="7">
+        <v>1235.5999999999999</v>
       </c>
       <c r="J31" s="7">
-        <v>-44.7</v>
+        <v>11.8</v>
       </c>
       <c r="K31" s="8">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="L31" s="9">
-        <v>31.6</v>
+        <v>1.28</v>
+      </c>
+      <c r="L31" s="7">
+        <v>29.6</v>
       </c>
       <c r="M31" s="8">
-        <v>8.6E-3</v>
-      </c>
-      <c r="N31" s="9">
-        <v>234.4</v>
+        <v>0.114</v>
+      </c>
+      <c r="N31" s="7">
+        <v>1235.5999999999999</v>
       </c>
       <c r="O31" s="7">
-        <v>-44.7</v>
+        <v>11.8</v>
       </c>
       <c r="P31" s="8">
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="Q31" s="9">
-        <v>31.6</v>
+        <v>1.28</v>
+      </c>
+      <c r="Q31" s="7">
+        <v>29.6</v>
       </c>
     </row>
     <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="11">
-        <v>45139</v>
+        <v>45170</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>17</v>
@@ -2875,39 +2875,39 @@
         <v>17</v>
       </c>
       <c r="H32" s="14">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="I32" s="13">
-        <v>-94.6</v>
+        <v>8.6E-3</v>
+      </c>
+      <c r="I32" s="15">
+        <v>234.4</v>
       </c>
       <c r="J32" s="13">
-        <v>-88.6</v>
+        <v>-44.7</v>
       </c>
       <c r="K32" s="14">
         <v>1.1599999999999999</v>
       </c>
       <c r="L32" s="15">
-        <v>33</v>
+        <v>31.6</v>
       </c>
       <c r="M32" s="14">
-        <v>2.5999999999999999E-3</v>
-      </c>
-      <c r="N32" s="13">
-        <v>-94.6</v>
+        <v>8.6E-3</v>
+      </c>
+      <c r="N32" s="15">
+        <v>234.4</v>
       </c>
       <c r="O32" s="13">
-        <v>-88.6</v>
+        <v>-44.7</v>
       </c>
       <c r="P32" s="14">
         <v>1.1599999999999999</v>
       </c>
       <c r="Q32" s="15">
-        <v>33</v>
+        <v>31.6</v>
       </c>
     </row>
     <row r="33" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
-        <v>45108</v>
+        <v>45139</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>17</v>
@@ -2928,33 +2928,86 @@
         <v>17</v>
       </c>
       <c r="H33" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="I33" s="9">
+        <v>-94.6</v>
+      </c>
+      <c r="J33" s="9">
+        <v>-88.6</v>
+      </c>
+      <c r="K33" s="8">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="L33" s="7">
+        <v>33</v>
+      </c>
+      <c r="M33" s="8">
+        <v>2.5999999999999999E-3</v>
+      </c>
+      <c r="N33" s="9">
+        <v>-94.6</v>
+      </c>
+      <c r="O33" s="9">
+        <v>-88.6</v>
+      </c>
+      <c r="P33" s="8">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="Q33" s="7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="11">
+        <v>45108</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H34" s="14">
         <v>4.7699999999999999E-2</v>
       </c>
-      <c r="I33" s="8" t="s">
+      <c r="I34" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J33" s="7">
+      <c r="J34" s="13">
         <v>-73.3</v>
       </c>
-      <c r="K33" s="8">
+      <c r="K34" s="14">
         <v>1.1499999999999999</v>
       </c>
-      <c r="L33" s="9">
+      <c r="L34" s="15">
         <v>36.200000000000003</v>
       </c>
-      <c r="M33" s="8">
+      <c r="M34" s="14">
         <v>4.7699999999999999E-2</v>
       </c>
-      <c r="N33" s="8" t="s">
+      <c r="N34" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="O33" s="7">
+      <c r="O34" s="13">
         <v>-73.3</v>
       </c>
-      <c r="P33" s="8">
+      <c r="P34" s="14">
         <v>1.1499999999999999</v>
       </c>
-      <c r="Q33" s="9">
+      <c r="Q34" s="15">
         <v>36.200000000000003</v>
       </c>
     </row>
